--- a/backend/data/Store, Order, Vehicle data.xlsx
+++ b/backend/data/Store, Order, Vehicle data.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayarzul.s/Documents/route-optimizations/distances/route_optimizer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayarzul.s/Documents/route/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA481DC4-EA82-C749-AD3D-A613BCD8E936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21A1E77-36D2-9F41-8A89-546B3189C42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-19020" windowWidth="28800" windowHeight="25340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="-18160" windowWidth="28800" windowHeight="25340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Store data" sheetId="7" r:id="rId1"/>
-    <sheet name="Store data old" sheetId="5" r:id="rId2"/>
+    <sheet name="Store" sheetId="5" r:id="rId2"/>
     <sheet name="Vehicle" sheetId="2" r:id="rId3"/>
     <sheet name="Vehicle UB" sheetId="8" r:id="rId4"/>
     <sheet name="Vehicle old" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Store!$A$1:$M$594</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Store data'!$A$1:$M$494</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Store data old'!$A$1:$M$594</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Vehicle!$A$1:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Vehicle old'!$A$1:$H$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Vehicle UB'!$A$1:$H$58</definedName>
